--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -879,13 +879,13 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,34 +896,34 @@
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>20</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>-25</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M15" s="15">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N15" s="15">
         <v>0</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-44.444444444444</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G16" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H16" s="15">
-        <v>-43.243243243243</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="I16" s="14">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K16" s="15">
-        <v>-40.384615384615</v>
+        <v>-31.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.592592592592</v>
+        <v>-32.786885245901</v>
       </c>
       <c r="M16" s="15">
-        <v>-44.642857142857</v>
+        <v>-31.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.470198675496</v>
+        <v>-75.739644970414</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-41.176470588235</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
         <v>61</v>
       </c>
       <c r="G17" s="14">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H17" s="15">
-        <v>8.928571428571</v>
+        <v>15.094339622641</v>
       </c>
       <c r="I17" s="14">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J17" s="14">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K17" s="15">
-        <v>10</v>
+        <v>8.602150537634</v>
       </c>
       <c r="L17" s="15">
-        <v>3.529411764705</v>
+        <v>1</v>
       </c>
       <c r="M17" s="15">
-        <v>137.837837837838</v>
+        <v>129.545454545455</v>
       </c>
       <c r="N17" s="15">
-        <v>18.918918918918</v>
+        <v>21.686746987951</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-62.5</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-27.272727272727</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K18" s="15">
-        <v>-18.518518518518</v>
+        <v>3.448275862068</v>
       </c>
       <c r="L18" s="15">
-        <v>-21.428571428571</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="M18" s="15">
-        <v>-40.540540540540</v>
+        <v>-25</v>
       </c>
       <c r="N18" s="15">
-        <v>-90</v>
+        <v>-88.28125</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H19" s="15">
-        <v>-25</v>
+        <v>-32.911392405063</v>
       </c>
       <c r="I19" s="14">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="J19" s="14">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.037735849056</v>
+        <v>-13.008130081300</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.819819819819</v>
+        <v>-15.079365079365</v>
       </c>
       <c r="M19" s="15">
-        <v>286.95652173913</v>
+        <v>282.142857142857</v>
       </c>
       <c r="N19" s="15">
-        <v>81.632653061224</v>
+        <v>81.355932203389</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D20" s="14">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>40</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F20" s="14">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G20" s="14">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H20" s="15">
-        <v>-1.612903225806</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I20" s="14">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J20" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K20" s="15">
-        <v>9.090909090909</v>
+        <v>8.139534883720</v>
       </c>
       <c r="L20" s="15">
-        <v>52.727272727272</v>
+        <v>45.3125</v>
       </c>
       <c r="M20" s="15">
-        <v>64.705882352941</v>
+        <v>63.157894736842</v>
       </c>
       <c r="N20" s="15">
-        <v>-50.877192982456</v>
+        <v>-50.793650793650</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D21" s="17">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>-19.736842105263</v>
+        <v>13.461538461538</v>
       </c>
       <c r="F21" s="17">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G21" s="17">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.358778625954</v>
+        <v>-12.941176470588</v>
       </c>
       <c r="I21" s="17">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="J21" s="17">
-        <v>350</v>
+        <v>402</v>
       </c>
       <c r="K21" s="18">
-        <v>-8</v>
+        <v>-4.975124378109</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.733727810650</v>
+        <v>-1.546391752577</v>
       </c>
       <c r="M21" s="18">
-        <v>52.60663507109</v>
+        <v>60.504201680672</v>
       </c>
       <c r="N21" s="18">
-        <v>-52.083333333333</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>75</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="L22" s="15">
-        <v>200</v>
+        <v>333.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>200</v>
+        <v>333.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>-54.545454545454</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I23" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J23" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" s="15">
-        <v>-21.428571428571</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-8.333333333333</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M23" s="15">
-        <v>266.666666666667</v>
+        <v>466.666666666667</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E24" s="15">
-        <v>39.130434782608</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="14">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G24" s="14">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H24" s="15">
-        <v>2.803738317757</v>
+        <v>-10.619469026548</v>
       </c>
       <c r="I24" s="14">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="J24" s="14">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="K24" s="15">
-        <v>4.895104895104</v>
+        <v>-3.932584269662</v>
       </c>
       <c r="L24" s="15">
-        <v>10.294117647058</v>
+        <v>8.917197452229</v>
       </c>
       <c r="M24" s="15">
-        <v>141.935483870968</v>
+        <v>140.845070422535</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,31 +1303,31 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H25" s="15">
-        <v>-56.666666666666</v>
+        <v>-44</v>
       </c>
       <c r="I25" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J25" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K25" s="15">
-        <v>-52.941176470588</v>
+        <v>-55</v>
       </c>
       <c r="L25" s="15">
         <v>-60</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E26" s="15">
-        <v>-36.842105263157</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G26" s="14">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.898550724637</v>
+        <v>-11.392405063291</v>
       </c>
       <c r="I26" s="14">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="J26" s="14">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.940594059405</v>
+        <v>-12.8</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.040404040404</v>
+        <v>-9.166666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>15.853658536585</v>
+        <v>7.920792079207</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F27" s="14">
+        <v>6</v>
+      </c>
+      <c r="G27" s="14">
         <v>7</v>
       </c>
-      <c r="G27" s="14">
-        <v>6</v>
-      </c>
       <c r="H27" s="15">
-        <v>16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-22.222222222222</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>4</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-75</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>-14.285714285714</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>22.222222222222</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L28" s="15">
-        <v>57.142857142857</v>
+        <v>37.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I29" s="14">
         <v>5</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>-37.5</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-37.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L30" s="15">
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>3</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -881,8 +881,8 @@
       <c r="L14" s="15">
         <v>200</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>50</v>
       </c>
       <c r="N14" s="15">
         <v>200</v>
@@ -896,37 +896,37 @@
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>-28.571428571428</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>-36.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M15" s="15">
-        <v>-22.222222222222</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G16" s="14">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>-28.205128205128</v>
+        <v>3.225806451612</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J16" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K16" s="15">
-        <v>-31.666666666666</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.786885245901</v>
+        <v>-29.577464788732</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.666666666666</v>
+        <v>-25.373134328358</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.739644970414</v>
+        <v>-74.489795918367</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
         <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G17" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H17" s="15">
-        <v>15.094339622641</v>
+        <v>-5.357142857142</v>
       </c>
       <c r="I17" s="14">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="J17" s="14">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="K17" s="15">
-        <v>8.602150537634</v>
+        <v>7.476635514018</v>
       </c>
       <c r="L17" s="15">
-        <v>1</v>
+        <v>6.481481481481</v>
       </c>
       <c r="M17" s="15">
-        <v>129.545454545455</v>
+        <v>121.153846153846</v>
       </c>
       <c r="N17" s="15">
-        <v>21.686746987951</v>
+        <v>16.161616161616</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>150</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
-        <v>-5.263157894736</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K18" s="15">
-        <v>3.448275862068</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L18" s="15">
-        <v>-3.225806451612</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="M18" s="15">
-        <v>-25</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.28125</v>
+        <v>-88.552188552188</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H19" s="15">
-        <v>-32.911392405063</v>
+        <v>-16</v>
       </c>
       <c r="I19" s="14">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="J19" s="14">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.008130081300</v>
+        <v>-7.913669064748</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.079365079365</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M19" s="15">
-        <v>282.142857142857</v>
+        <v>265.714285714286</v>
       </c>
       <c r="N19" s="15">
-        <v>81.355932203389</v>
+        <v>77.777777777777</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>44.444444444444</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F20" s="14">
         <v>54</v>
       </c>
       <c r="G20" s="14">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H20" s="15">
-        <v>-6.896551724137</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I20" s="14">
+        <v>100</v>
+      </c>
+      <c r="J20" s="14">
         <v>93</v>
       </c>
-      <c r="J20" s="14">
-        <v>86</v>
-      </c>
       <c r="K20" s="15">
-        <v>8.139534883720</v>
+        <v>7.526881720430</v>
       </c>
       <c r="L20" s="15">
-        <v>45.3125</v>
+        <v>38.888888888888</v>
       </c>
       <c r="M20" s="15">
-        <v>63.157894736842</v>
+        <v>63.934426229508</v>
       </c>
       <c r="N20" s="15">
-        <v>-50.793650793650</v>
+        <v>-52.830188679245</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D21" s="17">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E21" s="18">
-        <v>13.461538461538</v>
+        <v>-1.886792452830</v>
       </c>
       <c r="F21" s="17">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G21" s="17">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.941176470588</v>
+        <v>-8.606557377049</v>
       </c>
       <c r="I21" s="17">
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="J21" s="17">
-        <v>402</v>
+        <v>455</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.975124378109</v>
+        <v>-3.736263736263</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.546391752577</v>
+        <v>0.458715596330</v>
       </c>
       <c r="M21" s="18">
-        <v>60.504201680672</v>
+        <v>60.439560439560</v>
       </c>
       <c r="N21" s="18">
-        <v>-50</v>
+        <v>-50.564334085778</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>4</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>8</v>
-      </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
-      <c r="H22" s="15">
-        <v>166.666666666667</v>
+        <v>7</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>13</v>
@@ -1207,10 +1207,10 @@
         <v>225</v>
       </c>
       <c r="L22" s="15">
-        <v>333.333333333333</v>
+        <v>225</v>
       </c>
       <c r="M22" s="15">
-        <v>333.333333333333</v>
+        <v>225</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>-38.461538461538</v>
+        <v>-43.75</v>
       </c>
       <c r="I23" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="L23" s="15">
-        <v>21.428571428571</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M23" s="15">
-        <v>466.666666666667</v>
+        <v>375</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>29</v>
+      </c>
+      <c r="D24" s="14">
         <v>25</v>
       </c>
-      <c r="D24" s="14">
-        <v>35</v>
-      </c>
       <c r="E24" s="15">
-        <v>-28.571428571428</v>
+        <v>16</v>
       </c>
       <c r="F24" s="14">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G24" s="14">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.619469026548</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="J24" s="14">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.932584269662</v>
+        <v>-2.463054187192</v>
       </c>
       <c r="L24" s="15">
-        <v>8.917197452229</v>
+        <v>9.392265193370</v>
       </c>
       <c r="M24" s="15">
-        <v>140.845070422535</v>
+        <v>141.463414634146</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
         <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>-44</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I25" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J25" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K25" s="15">
-        <v>-55</v>
+        <v>-54.347826086956</v>
       </c>
       <c r="L25" s="15">
-        <v>-60</v>
+        <v>-58</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>46.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G26" s="14">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H26" s="15">
-        <v>-11.392405063291</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="J26" s="14">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.8</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L26" s="15">
-        <v>-9.166666666666</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M26" s="15">
-        <v>7.920792079207</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>-14.285714285714</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L27" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>-44.444444444444</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>-15.384615384615</v>
+        <v>-31.25</v>
       </c>
       <c r="L28" s="15">
         <v>37.5</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-37.5</v>
+        <v>-12.5</v>
       </c>
       <c r="M29" s="15">
-        <v>-37.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N29" s="15">
-        <v>-37.5</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>2</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
+        <v>7</v>
+      </c>
+      <c r="J30" s="14">
         <v>5</v>
       </c>
-      <c r="J30" s="14">
-        <v>4</v>
-      </c>
       <c r="K30" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L30" s="15">
+        <v>40</v>
+      </c>
+      <c r="M30" s="15">
         <v>0</v>
       </c>
-      <c r="M30" s="15">
-        <v>-16.666666666666</v>
-      </c>
       <c r="N30" s="15">
-        <v>-28.571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,35 +854,35 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>3</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>200</v>
       </c>
       <c r="L14" s="15">
         <v>200</v>
       </c>
       <c r="M14" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
         <v>200</v>
@@ -890,43 +890,43 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F15" s="14">
         <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-42.857142857142</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="L15" s="15">
-        <v>60</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M15" s="15">
-        <v>-27.272727272727</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N15" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F16" s="14">
+        <v>30</v>
+      </c>
+      <c r="G16" s="14">
         <v>32</v>
       </c>
-      <c r="G16" s="14">
-        <v>31</v>
-      </c>
       <c r="H16" s="15">
-        <v>3.225806451612</v>
+        <v>-6.25</v>
       </c>
       <c r="I16" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J16" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K16" s="15">
-        <v>-24.242424242424</v>
+        <v>-25.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.577464788732</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="M16" s="15">
-        <v>-25.373134328358</v>
+        <v>-25.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-74.489795918367</v>
+        <v>-74.311926605504</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
+        <v>-52.380952380952</v>
+      </c>
+      <c r="F17" s="14">
+        <v>50</v>
+      </c>
+      <c r="G17" s="14">
+        <v>65</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-23.076923076923</v>
+      </c>
+      <c r="I17" s="14">
+        <v>128</v>
+      </c>
+      <c r="J17" s="14">
+        <v>128</v>
+      </c>
+      <c r="K17" s="15">
         <v>0</v>
       </c>
-      <c r="F17" s="14">
-        <v>53</v>
-      </c>
-      <c r="G17" s="14">
-        <v>56</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-5.357142857142</v>
-      </c>
-      <c r="I17" s="14">
-        <v>115</v>
-      </c>
-      <c r="J17" s="14">
-        <v>107</v>
-      </c>
-      <c r="K17" s="15">
-        <v>7.476635514018</v>
-      </c>
       <c r="L17" s="15">
-        <v>6.481481481481</v>
+        <v>5.785123966942</v>
       </c>
       <c r="M17" s="15">
-        <v>121.153846153846</v>
+        <v>132.727272727273</v>
       </c>
       <c r="N17" s="15">
-        <v>16.161616161616</v>
+        <v>13.274336283185</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F18" s="14">
         <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="15">
-        <v>-26.086956521739</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J18" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.526315789473</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="L18" s="15">
-        <v>-2.857142857142</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="M18" s="15">
-        <v>-24.444444444444</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.552188552188</v>
+        <v>-88.323353293413</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
         <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H19" s="15">
-        <v>-16</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="I19" s="14">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="J19" s="14">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.913669064748</v>
+        <v>-7.189542483660</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.111111111111</v>
+        <v>-9.554140127388</v>
       </c>
       <c r="M19" s="15">
-        <v>265.714285714286</v>
+        <v>273.684210526316</v>
       </c>
       <c r="N19" s="15">
-        <v>77.777777777777</v>
+        <v>73.170731707317</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>54</v>
       </c>
       <c r="G20" s="14">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H20" s="15">
-        <v>3.846153846153</v>
+        <v>20</v>
       </c>
       <c r="I20" s="14">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J20" s="14">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K20" s="15">
-        <v>7.526881720430</v>
+        <v>4.901960784313</v>
       </c>
       <c r="L20" s="15">
-        <v>38.888888888888</v>
+        <v>27.380952380952</v>
       </c>
       <c r="M20" s="15">
-        <v>63.934426229508</v>
+        <v>59.701492537313</v>
       </c>
       <c r="N20" s="15">
-        <v>-52.830188679245</v>
+        <v>-55.230125523012</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E21" s="18">
-        <v>-1.886792452830</v>
+        <v>-23.728813559322</v>
       </c>
       <c r="F21" s="17">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G21" s="17">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.606557377049</v>
+        <v>-9.166666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>438</v>
+        <v>484</v>
       </c>
       <c r="J21" s="17">
-        <v>455</v>
+        <v>514</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.736263736263</v>
+        <v>-5.836575875486</v>
       </c>
       <c r="L21" s="18">
-        <v>0.458715596330</v>
+        <v>-1.626016260162</v>
       </c>
       <c r="M21" s="18">
-        <v>60.439560439560</v>
+        <v>64.625850340136</v>
       </c>
       <c r="N21" s="18">
-        <v>-50.564334085778</v>
+        <v>-51.454363089267</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="14">
         <v>7</v>
@@ -1195,25 +1195,25 @@
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I22" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="L22" s="15">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="M22" s="15">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>3</v>
+      </c>
+      <c r="D23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="14">
-        <v>5</v>
-      </c>
       <c r="E23" s="15">
-        <v>-60</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-43.75</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J23" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K23" s="15">
-        <v>-13.636363636363</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>35.714285714285</v>
+        <v>26.315789473684</v>
       </c>
       <c r="M23" s="15">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>16</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="14">
         <v>109</v>
       </c>
       <c r="G24" s="14">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-1.801801801801</v>
       </c>
       <c r="I24" s="14">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="J24" s="14">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.463054187192</v>
+        <v>-3.896103896103</v>
       </c>
       <c r="L24" s="15">
-        <v>9.392265193370</v>
+        <v>6.730769230769</v>
       </c>
       <c r="M24" s="15">
-        <v>141.463414634146</v>
+        <v>152.272727272727</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="14">
         <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>-29.411764705882</v>
+        <v>-40</v>
       </c>
       <c r="I25" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J25" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K25" s="15">
-        <v>-54.347826086956</v>
+        <v>-50.980392156862</v>
       </c>
       <c r="L25" s="15">
-        <v>-58</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>46.666666666666</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F26" s="14">
         <v>75</v>
       </c>
       <c r="G26" s="14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="I26" s="14">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="J26" s="14">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.142857142857</v>
+        <v>-3.086419753086</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.142857142857</v>
+        <v>-10.795454545454</v>
       </c>
       <c r="M26" s="15">
-        <v>11.111111111111</v>
+        <v>23.622047244094</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1388,160 +1388,160 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>-30.769230769230</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-72.727272727272</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-31.25</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L28" s="15">
-        <v>37.5</v>
+        <v>87.5</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I29" s="14">
         <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-12.5</v>
+        <v>-30</v>
       </c>
       <c r="M29" s="15">
         <v>-22.222222222222</v>
       </c>
       <c r="N29" s="15">
-        <v>-12.5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>2</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I30" s="14">
         <v>7</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,43 +890,43 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
+        <v>9</v>
+      </c>
+      <c r="G15" s="14">
         <v>4</v>
       </c>
-      <c r="G15" s="14">
-        <v>6</v>
-      </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>125</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
         <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>28.571428571428</v>
+        <v>114.285714285714</v>
       </c>
       <c r="M15" s="15">
-        <v>-18.181818181818</v>
+        <v>36.363636363636</v>
       </c>
       <c r="N15" s="15">
-        <v>-10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-44.444444444444</v>
+        <v>75</v>
       </c>
       <c r="F16" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H16" s="15">
-        <v>-6.25</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I16" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J16" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K16" s="15">
-        <v>-25.333333333333</v>
+        <v>-20.253164556962</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.205128205128</v>
+        <v>-21.25</v>
       </c>
       <c r="M16" s="15">
-        <v>-25.333333333333</v>
+        <v>-21.25</v>
       </c>
       <c r="N16" s="15">
-        <v>-74.311926605504</v>
+        <v>-74.180327868852</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
         <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>-52.380952380952</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="F17" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G17" s="14">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.076923076923</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="I17" s="14">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="J17" s="14">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-2.013422818791</v>
       </c>
       <c r="L17" s="15">
-        <v>5.785123966942</v>
+        <v>14.0625</v>
       </c>
       <c r="M17" s="15">
-        <v>132.727272727273</v>
+        <v>143.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>13.274336283185</v>
+        <v>8.955223880597</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-29.166666666666</v>
+        <v>-5</v>
       </c>
       <c r="I18" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K18" s="15">
-        <v>-9.302325581395</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.363636363636</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M18" s="15">
-        <v>-13.333333333333</v>
+        <v>-13.461538461538</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.323353293413</v>
+        <v>-87.704918032786</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="F19" s="14">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G19" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.970149253731</v>
+        <v>-10.294117647058</v>
       </c>
       <c r="I19" s="14">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J19" s="14">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.189542483660</v>
+        <v>-11.494252873563</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.554140127388</v>
+        <v>-10.465116279069</v>
       </c>
       <c r="M19" s="15">
-        <v>273.684210526316</v>
+        <v>234.782608695652</v>
       </c>
       <c r="N19" s="15">
-        <v>73.170731707317</v>
+        <v>55.555555555555</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F20" s="14">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G20" s="14">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H20" s="15">
-        <v>20</v>
+        <v>10.526315789473</v>
       </c>
       <c r="I20" s="14">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="J20" s="14">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="K20" s="15">
-        <v>4.901960784313</v>
+        <v>5.217391304347</v>
       </c>
       <c r="L20" s="15">
-        <v>27.380952380952</v>
+        <v>28.723404255319</v>
       </c>
       <c r="M20" s="15">
-        <v>59.701492537313</v>
+        <v>61.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-55.230125523012</v>
+        <v>-58.131487889273</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D21" s="17">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.728813559322</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F21" s="17">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G21" s="17">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.166666666666</v>
+        <v>-3.083700440528</v>
       </c>
       <c r="I21" s="17">
-        <v>484</v>
+        <v>547</v>
       </c>
       <c r="J21" s="17">
-        <v>514</v>
+        <v>577</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.836575875486</v>
+        <v>-5.199306759098</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.626016260162</v>
+        <v>2.626641651031</v>
       </c>
       <c r="M21" s="18">
-        <v>64.625850340136</v>
+        <v>67.278287461773</v>
       </c>
       <c r="N21" s="18">
-        <v>-51.454363089267</v>
+        <v>-52.227074235807</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>15</v>
@@ -1213,7 +1213,7 @@
         <v>150</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F23" s="14">
+        <v>16</v>
+      </c>
+      <c r="G23" s="14">
         <v>12</v>
       </c>
-      <c r="G23" s="14">
-        <v>14</v>
-      </c>
       <c r="H23" s="15">
-        <v>-14.285714285714</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J23" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L23" s="15">
-        <v>26.315789473684</v>
+        <v>45</v>
       </c>
       <c r="M23" s="15">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D24" s="14">
         <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>39.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G24" s="14">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.801801801801</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="J24" s="14">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.896103896103</v>
+        <v>0.386100386100</v>
       </c>
       <c r="L24" s="15">
-        <v>6.730769230769</v>
+        <v>13.537117903930</v>
       </c>
       <c r="M24" s="15">
-        <v>152.272727272727</v>
+        <v>152.427184466019</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>-40</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="I25" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J25" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K25" s="15">
-        <v>-50.980392156862</v>
+        <v>-49.056603773584</v>
       </c>
       <c r="L25" s="15">
-        <v>-54.545454545454</v>
+        <v>-54.237288135593</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15">
-        <v>27.272727272727</v>
+        <v>-8</v>
       </c>
       <c r="F26" s="14">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G26" s="14">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.25</v>
+        <v>1.162790697674</v>
       </c>
       <c r="I26" s="14">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="J26" s="14">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.086419753086</v>
+        <v>-4.278074866310</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.795454545454</v>
+        <v>-7.253886010362</v>
       </c>
       <c r="M26" s="15">
-        <v>23.622047244094</v>
+        <v>21.768707482993</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,163 +1385,163 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+        <v>6</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
         <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>300</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-37.5</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.764705882352</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L28" s="15">
-        <v>87.5</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="14">
+      <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29" s="14">
         <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L29" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="M29" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N29" s="15">
-        <v>-30</v>
+        <v>-27.272727272727</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="14">
+      <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30" s="14">
         <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N30" s="15">
-        <v>-22.222222222222</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,40 +860,40 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L14" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>6</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>125</v>
+        <v>700</v>
       </c>
       <c r="I15" s="14">
         <v>15</v>
@@ -920,13 +920,13 @@
         <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>114.285714285714</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>36.363636363636</v>
+        <v>25</v>
       </c>
       <c r="N15" s="15">
-        <v>25</v>
+        <v>7.142857142857</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E16" s="15">
-        <v>75</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G16" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>18.518518518518</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="I16" s="14">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J16" s="14">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K16" s="15">
-        <v>-20.253164556962</v>
+        <v>-24.175824175824</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.25</v>
+        <v>-24.175824175824</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.25</v>
+        <v>-19.767441860465</v>
       </c>
       <c r="N16" s="15">
-        <v>-74.180327868852</v>
+        <v>-74.632352941176</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" s="15">
-        <v>-19.047619047619</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="F17" s="14">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H17" s="15">
-        <v>-17.391304347826</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I17" s="14">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="J17" s="14">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.013422818791</v>
+        <v>-8.187134502923</v>
       </c>
       <c r="L17" s="15">
-        <v>14.0625</v>
+        <v>11.347517730496</v>
       </c>
       <c r="M17" s="15">
-        <v>143.333333333333</v>
+        <v>115.068493150685</v>
       </c>
       <c r="N17" s="15">
-        <v>8.955223880597</v>
+        <v>5.369127516778</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-5</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J18" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K18" s="15">
-        <v>-4.255319148936</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.764705882352</v>
+        <v>-20</v>
       </c>
       <c r="M18" s="15">
-        <v>-13.461538461538</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.704918032786</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>-47.619047619047</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F19" s="14">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H19" s="15">
-        <v>-10.294117647058</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I19" s="14">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="J19" s="14">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.494252873563</v>
+        <v>-14.507772020725</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.465116279069</v>
+        <v>-8.839779005524</v>
       </c>
       <c r="M19" s="15">
-        <v>234.782608695652</v>
+        <v>223.529411764706</v>
       </c>
       <c r="N19" s="15">
-        <v>55.555555555555</v>
+        <v>48.648648648648</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E20" s="15">
-        <v>7.692307692307</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G20" s="14">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H20" s="15">
-        <v>10.526315789473</v>
+        <v>-30.612244897959</v>
       </c>
       <c r="I20" s="14">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J20" s="14">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="K20" s="15">
-        <v>5.217391304347</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>28.723404255319</v>
+        <v>20</v>
       </c>
       <c r="M20" s="15">
-        <v>61.333333333333</v>
+        <v>55.555555555555</v>
       </c>
       <c r="N20" s="15">
-        <v>-58.131487889273</v>
+        <v>-60.501567398119</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.761904761904</v>
+        <v>-53.246753246753</v>
       </c>
       <c r="F21" s="17">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="G21" s="17">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.083700440528</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I21" s="17">
-        <v>547</v>
+        <v>584</v>
       </c>
       <c r="J21" s="17">
-        <v>577</v>
+        <v>654</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.199306759098</v>
+        <v>-10.703363914373</v>
       </c>
       <c r="L21" s="18">
-        <v>2.626641651031</v>
+        <v>-0.680272108843</v>
       </c>
       <c r="M21" s="18">
-        <v>67.278287461773</v>
+        <v>58.265582655826</v>
       </c>
       <c r="N21" s="18">
-        <v>-52.227074235807</v>
+        <v>-53.870458135861</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="L22" s="15">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="M22" s="15">
-        <v>150</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>33.333333333333</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I23" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J23" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K23" s="15">
-        <v>11.538461538461</v>
+        <v>17.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="M23" s="15">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>39</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E24" s="15">
-        <v>39.285714285714</v>
+        <v>21.875</v>
       </c>
       <c r="F24" s="14">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="G24" s="14">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>15.929203539823</v>
       </c>
       <c r="I24" s="14">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="J24" s="14">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="K24" s="15">
-        <v>0.386100386100</v>
+        <v>3.436426116838</v>
       </c>
       <c r="L24" s="15">
-        <v>13.537117903930</v>
+        <v>17.120622568093</v>
       </c>
       <c r="M24" s="15">
-        <v>152.427184466019</v>
+        <v>168.75</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>-42.105263157894</v>
+        <v>-40</v>
       </c>
       <c r="I25" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J25" s="14">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K25" s="15">
-        <v>-49.056603773584</v>
+        <v>-50</v>
       </c>
       <c r="L25" s="15">
-        <v>-54.237288135593</v>
+        <v>-50.819672131147</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D26" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G26" s="14">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H26" s="15">
-        <v>1.162790697674</v>
+        <v>11.363636363636</v>
       </c>
       <c r="I26" s="14">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="J26" s="14">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.278074866310</v>
+        <v>-3.755868544600</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.253886010362</v>
+        <v>-7.657657657657</v>
       </c>
       <c r="M26" s="15">
-        <v>21.768707482993</v>
+        <v>21.301775147929</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>6</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
         <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>6.666666666666</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>60</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>8</v>
-      </c>
       <c r="H28" s="15">
-        <v>-37.5</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-17.647058823529</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L28" s="15">
-        <v>55.555555555555</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,7 +1467,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J29" s="14">
         <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>14.285714285714</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L29" s="15">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="M29" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-27.272727272727</v>
+        <v>-26.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,7 +1508,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,31 +1517,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I30" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J30" s="14">
         <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M30" s="15">
-        <v>14.285714285714</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N30" s="15">
-        <v>-20</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -851,369 +851,369 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>4</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L14" s="15">
         <v>300</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N14" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I15" s="14">
         <v>15</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>25</v>
+        <v>15.384615384615</v>
       </c>
       <c r="N15" s="15">
-        <v>7.142857142857</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F16" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H16" s="15">
-        <v>-12.903225806451</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I16" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J16" s="14">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K16" s="15">
-        <v>-24.175824175824</v>
+        <v>-27</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.175824175824</v>
+        <v>-30.476190476190</v>
       </c>
       <c r="M16" s="15">
-        <v>-19.767441860465</v>
+        <v>-19.780219780219</v>
       </c>
       <c r="N16" s="15">
-        <v>-74.632352941176</v>
+        <v>-75.827814569536</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>-59.090909090909</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G17" s="14">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17" s="15">
-        <v>-30.769230769230</v>
+        <v>-39.240506329113</v>
       </c>
       <c r="I17" s="14">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J17" s="14">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="K17" s="15">
-        <v>-8.187134502923</v>
+        <v>-9.139784946236</v>
       </c>
       <c r="L17" s="15">
-        <v>11.347517730496</v>
+        <v>11.184210526315</v>
       </c>
       <c r="M17" s="15">
-        <v>115.068493150685</v>
+        <v>108.641975308642</v>
       </c>
       <c r="N17" s="15">
-        <v>5.369127516778</v>
+        <v>1.807228915662</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-22.727272727272</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I18" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K18" s="15">
-        <v>-5.882352941176</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="L18" s="15">
-        <v>-20</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.580645161290</v>
+        <v>-17.460317460317</v>
       </c>
       <c r="N18" s="15">
-        <v>-88</v>
+        <v>-87.706855791962</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-36.842105263157</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H19" s="15">
-        <v>-21.428571428571</v>
+        <v>-26.760563380281</v>
       </c>
       <c r="I19" s="14">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="J19" s="14">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="K19" s="15">
-        <v>-14.507772020725</v>
+        <v>-13.809523809523</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.839779005524</v>
+        <v>-5.729166666666</v>
       </c>
       <c r="M19" s="15">
-        <v>223.529411764706</v>
+        <v>217.543859649123</v>
       </c>
       <c r="N19" s="15">
-        <v>48.648648648648</v>
+        <v>50.833333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D20" s="14">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G20" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H20" s="15">
-        <v>-30.612244897959</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J20" s="14">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K20" s="15">
-        <v>-6.666666666666</v>
+        <v>-8.843537414965</v>
       </c>
       <c r="L20" s="15">
-        <v>20</v>
+        <v>15.517241379310</v>
       </c>
       <c r="M20" s="15">
-        <v>55.555555555555</v>
+        <v>54.022988505747</v>
       </c>
       <c r="N20" s="15">
-        <v>-60.501567398119</v>
+        <v>-61.494252873563</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="E21" s="18">
-        <v>-53.246753246753</v>
+        <v>-29.508196721311</v>
       </c>
       <c r="F21" s="17">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="G21" s="17">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.222222222222</v>
+        <v>-29.230769230769</v>
       </c>
       <c r="I21" s="17">
-        <v>584</v>
+        <v>628</v>
       </c>
       <c r="J21" s="17">
-        <v>654</v>
+        <v>715</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.703363914373</v>
+        <v>-12.167832167832</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.680272108843</v>
+        <v>-2.484472049689</v>
       </c>
       <c r="M21" s="18">
-        <v>58.265582655826</v>
+        <v>58.186397984886</v>
       </c>
       <c r="N21" s="18">
-        <v>-53.870458135861</v>
+        <v>-54.393609295570</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="H22" s="15">
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="L22" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M22" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
-      </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>36.363636363636</v>
+        <v>116.666666666667</v>
       </c>
       <c r="I23" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J23" s="14">
         <v>28</v>
       </c>
       <c r="K23" s="15">
-        <v>17.857142857142</v>
+        <v>32.142857142857</v>
       </c>
       <c r="L23" s="15">
-        <v>32</v>
+        <v>37.037037037037</v>
       </c>
       <c r="M23" s="15">
-        <v>560</v>
+        <v>428.571428571429</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E24" s="15">
-        <v>21.875</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G24" s="14">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="H24" s="15">
-        <v>15.929203539823</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="J24" s="14">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="K24" s="15">
-        <v>3.436426116838</v>
+        <v>-0.611620795107</v>
       </c>
       <c r="L24" s="15">
-        <v>17.120622568093</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M24" s="15">
-        <v>168.75</v>
+        <v>146.212121212121</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1306,37 +1306,37 @@
         <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-57.142857142857</v>
+        <v>-70</v>
       </c>
       <c r="F25" s="14">
         <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H25" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J25" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K25" s="15">
-        <v>-50</v>
+        <v>-52.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>-50.819672131147</v>
+        <v>-48.4375</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,204 +1344,204 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>5.882352941176</v>
       </c>
       <c r="F26" s="14">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G26" s="14">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H26" s="15">
-        <v>11.363636363636</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="J26" s="14">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.755868544600</v>
+        <v>-2.608695652173</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.657657657657</v>
+        <v>-4.273504273504</v>
       </c>
       <c r="M26" s="15">
-        <v>21.301775147929</v>
+        <v>17.277486910994</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>166.666666666667</v>
+        <v>125</v>
       </c>
       <c r="I27" s="14">
+        <v>19</v>
+      </c>
+      <c r="J27" s="14">
         <v>17</v>
       </c>
-      <c r="J27" s="14">
-        <v>15</v>
-      </c>
       <c r="K27" s="15">
-        <v>13.333333333333</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L27" s="15">
-        <v>41.666666666666</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14">
+        <v>4</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="15">
+        <v>100</v>
+      </c>
+      <c r="I28" s="14">
+        <v>17</v>
+      </c>
+      <c r="J28" s="14">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>4</v>
-      </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-20</v>
-      </c>
-      <c r="I28" s="14">
-        <v>13</v>
-      </c>
-      <c r="J28" s="14">
-        <v>18</v>
-      </c>
       <c r="K28" s="15">
-        <v>-27.777777777777</v>
+        <v>-15</v>
       </c>
       <c r="L28" s="15">
-        <v>44.444444444444</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>3</v>
-      </c>
-      <c r="D29" s="13" t="s">
+      <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
         <v>11</v>
       </c>
       <c r="J29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K29" s="15">
-        <v>57.142857142857</v>
+        <v>37.5</v>
       </c>
       <c r="L29" s="15">
         <v>10</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N29" s="15">
-        <v>-26.666666666666</v>
+        <v>-35.294117647058</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>2</v>
-      </c>
-      <c r="D30" s="13" t="s">
+      <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I30" s="14">
         <v>10</v>
       </c>
       <c r="J30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L30" s="15">
         <v>42.857142857142</v>
       </c>
       <c r="M30" s="15">
-        <v>11.111111111111</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N30" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>1236</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>708</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>1682</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>625</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>2746</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>7097</v>

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>4</v>
@@ -885,335 +885,335 @@
         <v>-20</v>
       </c>
       <c r="N14" s="15">
-        <v>100</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>7</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>15.384615384615</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>15.384615384615</v>
+        <v>23.076923076923</v>
       </c>
       <c r="N15" s="15">
-        <v>-6.25</v>
+        <v>-5.882352941176</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-55.555555555555</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>-35.294117647058</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="I16" s="14">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J16" s="14">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K16" s="15">
-        <v>-27</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.476190476190</v>
+        <v>-28.695652173913</v>
       </c>
       <c r="M16" s="15">
-        <v>-19.780219780219</v>
+        <v>-15.463917525773</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.827814569536</v>
+        <v>-75.882352941176</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E17" s="15">
-        <v>-26.666666666666</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G17" s="14">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H17" s="15">
-        <v>-39.240506329113</v>
+        <v>-32.926829268292</v>
       </c>
       <c r="I17" s="14">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="J17" s="14">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.139784946236</v>
+        <v>-10.952380952381</v>
       </c>
       <c r="L17" s="15">
-        <v>11.184210526315</v>
+        <v>14.024390243902</v>
       </c>
       <c r="M17" s="15">
-        <v>108.641975308642</v>
+        <v>110.112359550562</v>
       </c>
       <c r="N17" s="15">
-        <v>1.807228915662</v>
+        <v>5.056179775280</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-5.263157894736</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J18" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K18" s="15">
-        <v>-8.771929824561</v>
+        <v>-10.9375</v>
       </c>
       <c r="L18" s="15">
-        <v>-23.529411764705</v>
+        <v>-21.917808219178</v>
       </c>
       <c r="M18" s="15">
-        <v>-17.460317460317</v>
+        <v>-16.176470588235</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.706855791962</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.764705882352</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H19" s="15">
-        <v>-26.760563380281</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I19" s="14">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="J19" s="14">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.809523809523</v>
+        <v>-10.683760683760</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.729166666666</v>
+        <v>-0.476190476190</v>
       </c>
       <c r="M19" s="15">
-        <v>217.543859649123</v>
+        <v>237.096774193548</v>
       </c>
       <c r="N19" s="15">
-        <v>50.833333333333</v>
+        <v>53.676470588235</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D20" s="14">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E20" s="15">
-        <v>-25</v>
+        <v>-35</v>
       </c>
       <c r="F20" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G20" s="14">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I20" s="14">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="J20" s="14">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="K20" s="15">
-        <v>-8.843537414965</v>
+        <v>-11.976047904191</v>
       </c>
       <c r="L20" s="15">
-        <v>15.517241379310</v>
+        <v>21.487603305785</v>
       </c>
       <c r="M20" s="15">
-        <v>54.022988505747</v>
+        <v>65.168539325842</v>
       </c>
       <c r="N20" s="15">
-        <v>-61.494252873563</v>
+        <v>-61.213720316622</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="D21" s="17">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="E21" s="18">
-        <v>-29.508196721311</v>
+        <v>-20.238095238095</v>
       </c>
       <c r="F21" s="17">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="G21" s="17">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.230769230769</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>628</v>
+        <v>702</v>
       </c>
       <c r="J21" s="17">
-        <v>715</v>
+        <v>799</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.167832167832</v>
+        <v>-12.140175219023</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.484472049689</v>
+        <v>0.862068965517</v>
       </c>
       <c r="M21" s="18">
-        <v>58.186397984886</v>
+        <v>65.957446808510</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.393609295570</v>
+        <v>-53.540701522170</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="14">
-        <v>2</v>
+        <v>29</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>16</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
+        <v>166.666666666667</v>
+      </c>
+      <c r="L22" s="15">
         <v>220</v>
-      </c>
-      <c r="L22" s="15">
-        <v>300</v>
       </c>
       <c r="M22" s="15">
         <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>29</v>
+        <v>4</v>
+      </c>
+      <c r="D23" s="14">
+        <v>4</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>116.666666666667</v>
+        <v>75</v>
       </c>
       <c r="I23" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J23" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K23" s="15">
-        <v>32.142857142857</v>
+        <v>28.125</v>
       </c>
       <c r="L23" s="15">
-        <v>37.037037037037</v>
+        <v>36.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>428.571428571429</v>
+        <v>355.555555555556</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="F24" s="14">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="G24" s="14">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>4.511278195488</v>
       </c>
       <c r="I24" s="14">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="J24" s="14">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.611620795107</v>
+        <v>-1.098901098901</v>
       </c>
       <c r="L24" s="15">
-        <v>18.181818181818</v>
+        <v>22.866894197952</v>
       </c>
       <c r="M24" s="15">
-        <v>146.212121212121</v>
+        <v>153.521126760563</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-70</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H25" s="15">
         <v>-50</v>
       </c>
       <c r="I25" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J25" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K25" s="15">
-        <v>-52.857142857142</v>
+        <v>-50.649350649350</v>
       </c>
       <c r="L25" s="15">
-        <v>-48.4375</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15">
-        <v>5.882352941176</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F26" s="14">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G26" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H26" s="15">
-        <v>6.666666666666</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="I26" s="14">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="J26" s="14">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.608695652173</v>
+        <v>-3.90625</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.273504273504</v>
+        <v>-1.6</v>
       </c>
       <c r="M26" s="15">
-        <v>17.277486910994</v>
+        <v>14.418604651162</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1394,31 +1394,31 @@
         <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
+        <v>20</v>
+      </c>
+      <c r="J27" s="14">
         <v>19</v>
       </c>
-      <c r="J27" s="14">
-        <v>17</v>
-      </c>
       <c r="K27" s="15">
-        <v>11.764705882352</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L27" s="15">
-        <v>35.714285714285</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>-15</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L28" s="15">
-        <v>41.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I29" s="14">
         <v>11</v>
@@ -1497,10 +1497,10 @@
         <v>10</v>
       </c>
       <c r="M29" s="15">
-        <v>-15.384615384615</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="N29" s="15">
-        <v>-35.294117647058</v>
+        <v>-52.173913043478</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I30" s="14">
         <v>10</v>
@@ -1538,10 +1538,10 @@
         <v>42.857142857142</v>
       </c>
       <c r="M30" s="15">
-        <v>-9.090909090909</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-37.5</v>
+        <v>-52.380952380952</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>1236</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>708</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>1682</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>625</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>2746</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>7097</v>

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -199,13 +199,13 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -851,82 +851,82 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M14" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-20</v>
+        <v>-44.444444444444</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="D15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" s="14">
         <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>14.285714285714</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>30.769230769230</v>
       </c>
       <c r="M15" s="15">
-        <v>23.076923076923</v>
+        <v>21.428571428571</v>
       </c>
       <c r="N15" s="15">
-        <v>-5.882352941176</v>
+        <v>-10.526315789473</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H16" s="15">
-        <v>-21.212121212121</v>
+        <v>-44.186046511627</v>
       </c>
       <c r="I16" s="14">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J16" s="14">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="K16" s="15">
-        <v>-24.074074074074</v>
+        <v>-28.688524590163</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.695652173913</v>
+        <v>-28.099173553719</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.463917525773</v>
+        <v>-18.691588785046</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.882352941176</v>
+        <v>-75.966850828729</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
         <v>24</v>
       </c>
       <c r="E17" s="15">
-        <v>-29.166666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
         <v>55</v>
       </c>
       <c r="G17" s="14">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H17" s="15">
-        <v>-32.926829268292</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I17" s="14">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="J17" s="14">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.952380952381</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="L17" s="15">
-        <v>14.024390243902</v>
+        <v>17.919075144508</v>
       </c>
       <c r="M17" s="15">
-        <v>110.112359550562</v>
+        <v>106.060606060606</v>
       </c>
       <c r="N17" s="15">
-        <v>5.056179775280</v>
+        <v>9.090909090909</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
         <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.047619047619</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J18" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.9375</v>
+        <v>-11.267605633802</v>
       </c>
       <c r="L18" s="15">
-        <v>-21.917808219178</v>
+        <v>-16</v>
       </c>
       <c r="M18" s="15">
-        <v>-16.176470588235</v>
+        <v>-11.267605633802</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.5</v>
+        <v>-87.374749498998</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F19" s="14">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G19" s="14">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.222222222222</v>
+        <v>-12.857142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="J19" s="14">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.683760683760</v>
+        <v>-10.245901639344</v>
       </c>
       <c r="L19" s="15">
-        <v>-0.476190476190</v>
+        <v>-2.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>237.096774193548</v>
+        <v>231.818181818182</v>
       </c>
       <c r="N19" s="15">
-        <v>53.676470588235</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E20" s="15">
-        <v>-35</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F20" s="14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G20" s="14">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H20" s="15">
-        <v>-38.461538461538</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="I20" s="14">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="J20" s="14">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="K20" s="15">
-        <v>-11.976047904191</v>
+        <v>-16.304347826087</v>
       </c>
       <c r="L20" s="15">
-        <v>21.487603305785</v>
+        <v>18.461538461538</v>
       </c>
       <c r="M20" s="15">
-        <v>65.168539325842</v>
+        <v>55.555555555555</v>
       </c>
       <c r="N20" s="15">
-        <v>-61.213720316622</v>
+        <v>-62.980769230769</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.238095238095</v>
+        <v>-35.616438356164</v>
       </c>
       <c r="F21" s="17">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="G21" s="17">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.666666666666</v>
+        <v>-33.559322033898</v>
       </c>
       <c r="I21" s="17">
-        <v>702</v>
+        <v>749</v>
       </c>
       <c r="J21" s="17">
-        <v>799</v>
+        <v>872</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.140175219023</v>
+        <v>-14.105504587156</v>
       </c>
       <c r="L21" s="18">
-        <v>0.862068965517</v>
+        <v>1.490514905149</v>
       </c>
       <c r="M21" s="18">
-        <v>65.957446808510</v>
+        <v>62.472885032538</v>
       </c>
       <c r="N21" s="18">
-        <v>-53.540701522170</v>
+        <v>-54.273504273504</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
@@ -1192,28 +1192,28 @@
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>16</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
+        <v>128.571428571429</v>
+      </c>
+      <c r="L22" s="15">
         <v>166.666666666667</v>
       </c>
-      <c r="L22" s="15">
-        <v>220</v>
-      </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F23" s="14">
+        <v>11</v>
+      </c>
+      <c r="G23" s="14">
         <v>14</v>
       </c>
-      <c r="G23" s="14">
-        <v>8</v>
-      </c>
       <c r="H23" s="15">
-        <v>75</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I23" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J23" s="14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K23" s="15">
-        <v>28.125</v>
+        <v>7.5</v>
       </c>
       <c r="L23" s="15">
-        <v>36.666666666666</v>
+        <v>38.709677419354</v>
       </c>
       <c r="M23" s="15">
-        <v>355.555555555556</v>
+        <v>377.777777777778</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-5.405405405405</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F24" s="14">
         <v>139</v>
       </c>
       <c r="G24" s="14">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="15">
-        <v>4.511278195488</v>
+        <v>0.724637681159</v>
       </c>
       <c r="I24" s="14">
-        <v>360</v>
+        <v>399</v>
       </c>
       <c r="J24" s="14">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.098901098901</v>
+        <v>0.503778337531</v>
       </c>
       <c r="L24" s="15">
-        <v>22.866894197952</v>
+        <v>28.295819935691</v>
       </c>
       <c r="M24" s="15">
-        <v>153.521126760563</v>
+        <v>155.769230769231</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1306,37 +1306,37 @@
         <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-28.571428571428</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H25" s="15">
-        <v>-50</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="I25" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J25" s="14">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K25" s="15">
-        <v>-50.649350649350</v>
+        <v>-46.25</v>
       </c>
       <c r="L25" s="15">
-        <v>-45.714285714285</v>
+        <v>-41.095890410958</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D26" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.384615384615</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="F26" s="14">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G26" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H26" s="15">
-        <v>-4.255319148936</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I26" s="14">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="J26" s="14">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.90625</v>
+        <v>-4.844290657439</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.6</v>
+        <v>2.996254681647</v>
       </c>
       <c r="M26" s="15">
-        <v>14.418604651162</v>
+        <v>13.636363636363</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1387,38 +1387,38 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+      <c r="D27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" s="14">
         <v>19</v>
       </c>
       <c r="K27" s="15">
-        <v>5.263157894736</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>23.529411764705</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,163 +1426,163 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.181818181818</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>5.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-50</v>
       </c>
       <c r="F29" s="14">
         <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>300</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I29" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J29" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K29" s="15">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="L29" s="15">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M29" s="15">
-        <v>-21.428571428571</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="N29" s="15">
-        <v>-52.173913043478</v>
+        <v>-55.172413793103</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-50</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>42.857142857142</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L30" s="15">
-        <v>42.857142857142</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M30" s="15">
-        <v>-16.666666666666</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-52.380952380952</v>
+        <v>-59.259259259259</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
+      </c>
+      <c r="G31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="H31" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="14">
+        <v>1</v>
+      </c>
+      <c r="J31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1608,40 +1608,40 @@
         <v>40</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -199,13 +199,13 @@
     <t>Murder</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -851,23 +851,23 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="14">
         <v>1</v>
-      </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14">
-        <v>2</v>
       </c>
       <c r="G14" s="14">
         <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>5</v>
@@ -882,51 +882,51 @@
         <v>400</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>22</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>21.428571428571</v>
+        <v>20</v>
       </c>
       <c r="L15" s="15">
-        <v>30.769230769230</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M15" s="15">
-        <v>21.428571428571</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N15" s="15">
-        <v>-10.526315789473</v>
+        <v>-14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E16" s="15">
-        <v>-57.142857142857</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="F16" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H16" s="15">
-        <v>-44.186046511627</v>
+        <v>-52.083333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J16" s="14">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="K16" s="15">
-        <v>-28.688524590163</v>
+        <v>-33.812949640287</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.099173553719</v>
+        <v>-28.125</v>
       </c>
       <c r="M16" s="15">
-        <v>-18.691588785046</v>
+        <v>-18.584070796460</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.966850828729</v>
+        <v>-76.165803108808</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="F17" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G17" s="14">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H17" s="15">
-        <v>-35.294117647058</v>
+        <v>-35.164835164835</v>
       </c>
       <c r="I17" s="14">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="J17" s="14">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="K17" s="15">
-        <v>-12.820512820512</v>
+        <v>-16.030534351145</v>
       </c>
       <c r="L17" s="15">
-        <v>17.919075144508</v>
+        <v>13.402061855670</v>
       </c>
       <c r="M17" s="15">
-        <v>106.060606060606</v>
+        <v>101.834862385321</v>
       </c>
       <c r="N17" s="15">
-        <v>9.090909090909</v>
+        <v>10.552763819095</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
         <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H18" s="15">
-        <v>-20.833333333333</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="I18" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J18" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.267605633802</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="L18" s="15">
-        <v>-16</v>
+        <v>-16.25</v>
       </c>
       <c r="M18" s="15">
-        <v>-11.267605633802</v>
+        <v>-19.277108433734</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.374749498998</v>
+        <v>-87.115384615384</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>10</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F19" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G19" s="14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.857142857142</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="J19" s="14">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.245901639344</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.666666666666</v>
+        <v>-3.305785123966</v>
       </c>
       <c r="M19" s="15">
-        <v>231.818181818182</v>
+        <v>234.285714285714</v>
       </c>
       <c r="N19" s="15">
-        <v>50</v>
+        <v>50.967741935483</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D20" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15">
-        <v>-58.823529411764</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G20" s="14">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H20" s="15">
-        <v>-52.173913043478</v>
+        <v>-39.344262295082</v>
       </c>
       <c r="I20" s="14">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="J20" s="14">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.304347826087</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="L20" s="15">
-        <v>18.461538461538</v>
+        <v>10.273972602739</v>
       </c>
       <c r="M20" s="15">
-        <v>55.555555555555</v>
+        <v>59.405940594059</v>
       </c>
       <c r="N20" s="15">
-        <v>-62.980769230769</v>
+        <v>-64.301552106430</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D21" s="17">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E21" s="18">
-        <v>-35.616438356164</v>
+        <v>-37.179487179487</v>
       </c>
       <c r="F21" s="17">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="G21" s="17">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H21" s="18">
-        <v>-33.559322033898</v>
+        <v>-30.067567567567</v>
       </c>
       <c r="I21" s="17">
-        <v>749</v>
+        <v>797</v>
       </c>
       <c r="J21" s="17">
-        <v>872</v>
+        <v>950</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.105504587156</v>
+        <v>-16.105263157894</v>
       </c>
       <c r="L21" s="18">
-        <v>1.490514905149</v>
+        <v>-0.993788819875</v>
       </c>
       <c r="M21" s="18">
-        <v>62.472885032538</v>
+        <v>60.685483870967</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.273504273504</v>
+        <v>-54.247990815155</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
@@ -1192,19 +1192,19 @@
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>16</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>128.571428571429</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
         <v>166.666666666667</v>
@@ -1213,7 +1213,7 @@
         <v>77.777777777777</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1224,37 +1224,37 @@
         <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="F23" s="14">
         <v>11</v>
       </c>
       <c r="G23" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>-21.428571428571</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I23" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J23" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K23" s="15">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>38.709677419354</v>
+        <v>32.352941176470</v>
       </c>
       <c r="M23" s="15">
-        <v>377.777777777778</v>
+        <v>400</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>9.090909090909</v>
+        <v>-4</v>
       </c>
       <c r="F24" s="14">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="G24" s="14">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H24" s="15">
-        <v>0.724637681159</v>
+        <v>-4.580152671755</v>
       </c>
       <c r="I24" s="14">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="J24" s="14">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="K24" s="15">
-        <v>0.503778337531</v>
+        <v>0.473933649289</v>
       </c>
       <c r="L24" s="15">
-        <v>28.295819935691</v>
+        <v>26.190476190476</v>
       </c>
       <c r="M24" s="15">
-        <v>155.769230769231</v>
+        <v>147.953216374269</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1306,37 +1306,37 @@
         <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>150</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H25" s="15">
-        <v>-40.740740740740</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I25" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J25" s="14">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K25" s="15">
-        <v>-46.25</v>
+        <v>-41.463414634146</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.095890410958</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.121212121212</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="14">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G26" s="14">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.882352941176</v>
+        <v>-2.127659574468</v>
       </c>
       <c r="I26" s="14">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="J26" s="14">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.844290657439</v>
+        <v>-3.257328990228</v>
       </c>
       <c r="L26" s="15">
-        <v>2.996254681647</v>
+        <v>3.125</v>
       </c>
       <c r="M26" s="15">
-        <v>13.636363636363</v>
+        <v>14.230769230769</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1387,38 +1387,38 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="13" t="s">
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-20</v>
+      </c>
+      <c r="I27" s="14">
         <v>22</v>
       </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>4</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-25</v>
-      </c>
-      <c r="I27" s="14">
-        <v>21</v>
-      </c>
       <c r="J27" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K27" s="15">
-        <v>10.526315789473</v>
+        <v>10</v>
       </c>
       <c r="L27" s="15">
-        <v>23.529411764705</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1429,60 +1429,60 @@
         <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K28" s="15">
-        <v>-17.391304347826</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="15">
-        <v>5.555555555555</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F29" s="14">
-        <v>4</v>
       </c>
       <c r="G29" s="14">
         <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I29" s="14">
         <v>13</v>
@@ -1497,33 +1497,33 @@
         <v>30</v>
       </c>
       <c r="M29" s="15">
-        <v>-7.142857142857</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-55.172413793103</v>
+        <v>-59.375</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F30" s="14">
-        <v>3</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I30" s="14">
         <v>11</v>
@@ -1538,51 +1538,51 @@
         <v>57.142857142857</v>
       </c>
       <c r="M30" s="15">
-        <v>-8.333333333333</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N30" s="15">
-        <v>-59.259259259259</v>
+        <v>-63.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>21</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -873,33 +873,33 @@
         <v>5</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L14" s="15">
         <v>400</v>
       </c>
       <c r="M14" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N14" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="14">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
@@ -914,188 +914,188 @@
         <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" s="15">
+        <v>12.5</v>
+      </c>
+      <c r="L15" s="15">
         <v>20</v>
       </c>
-      <c r="L15" s="15">
-        <v>28.571428571428</v>
-      </c>
       <c r="M15" s="15">
-        <v>28.571428571428</v>
+        <v>20</v>
       </c>
       <c r="N15" s="15">
-        <v>-14.285714285714</v>
+        <v>-18.181818181818</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>-70.588235294117</v>
+        <v>-30</v>
       </c>
       <c r="F16" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H16" s="15">
-        <v>-52.083333333333</v>
+        <v>-46.938775510204</v>
       </c>
       <c r="I16" s="14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J16" s="14">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.812949640287</v>
+        <v>-32.885906040268</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.125</v>
+        <v>-28.057553956834</v>
       </c>
       <c r="M16" s="15">
-        <v>-18.584070796460</v>
+        <v>-18.032786885245</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.165803108808</v>
+        <v>-75.609756097561</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="14">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>15</v>
-      </c>
       <c r="D17" s="14">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>-46.428571428571</v>
+        <v>41.176470588235</v>
       </c>
       <c r="F17" s="14">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="G17" s="14">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H17" s="15">
-        <v>-35.164835164835</v>
+        <v>-21.505376344086</v>
       </c>
       <c r="I17" s="14">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="J17" s="14">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="K17" s="15">
-        <v>-16.030534351145</v>
+        <v>-11.469534050179</v>
       </c>
       <c r="L17" s="15">
-        <v>13.402061855670</v>
+        <v>19.323671497584</v>
       </c>
       <c r="M17" s="15">
-        <v>101.834862385321</v>
+        <v>109.322033898305</v>
       </c>
       <c r="N17" s="15">
-        <v>10.552763819095</v>
+        <v>17.619047619047</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
+        <v>5</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-40</v>
+      </c>
+      <c r="F18" s="14">
+        <v>17</v>
+      </c>
+      <c r="G18" s="14">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>4</v>
-      </c>
-      <c r="D18" s="14">
-        <v>6</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F18" s="14">
-        <v>19</v>
-      </c>
-      <c r="G18" s="14">
-        <v>26</v>
-      </c>
       <c r="H18" s="15">
-        <v>-26.923076923076</v>
+        <v>-32</v>
       </c>
       <c r="I18" s="14">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J18" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K18" s="15">
-        <v>-12.987012987013</v>
+        <v>-14.634146341463</v>
       </c>
       <c r="L18" s="15">
-        <v>-16.25</v>
+        <v>-19.540229885057</v>
       </c>
       <c r="M18" s="15">
-        <v>-19.277108433734</v>
+        <v>-21.348314606741</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.115384615384</v>
+        <v>-87.318840579710</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
         <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>7.142857142857</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="F19" s="14">
         <v>65</v>
       </c>
       <c r="G19" s="14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I19" s="14">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="J19" s="14">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.302325581395</v>
+        <v>-11.071428571428</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.305785123966</v>
+        <v>-3.861003861003</v>
       </c>
       <c r="M19" s="15">
-        <v>234.285714285714</v>
+        <v>232</v>
       </c>
       <c r="N19" s="15">
-        <v>50.967741935483</v>
+        <v>52.760736196319</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
         <v>9</v>
@@ -1107,113 +1107,113 @@
         <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" s="14">
         <v>61</v>
       </c>
       <c r="H20" s="15">
-        <v>-39.344262295082</v>
+        <v>-37.704918032786</v>
       </c>
       <c r="I20" s="14">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J20" s="14">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.857142857142</v>
+        <v>-18.269230769230</v>
       </c>
       <c r="L20" s="15">
-        <v>10.273972602739</v>
+        <v>11.842105263157</v>
       </c>
       <c r="M20" s="15">
-        <v>59.405940594059</v>
+        <v>50.442477876106</v>
       </c>
       <c r="N20" s="15">
-        <v>-64.301552106430</v>
+        <v>-64.360587002096</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D21" s="17">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E21" s="18">
-        <v>-37.179487179487</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="F21" s="17">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="G21" s="17">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.067567567567</v>
+        <v>-26.402640264026</v>
       </c>
       <c r="I21" s="17">
-        <v>797</v>
+        <v>859</v>
       </c>
       <c r="J21" s="17">
-        <v>950</v>
+        <v>1018</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.105263157894</v>
+        <v>-15.618860510805</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.993788819875</v>
+        <v>-0.116279069767</v>
       </c>
       <c r="M21" s="18">
-        <v>60.685483870967</v>
+        <v>59.369202226345</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.247990815155</v>
+        <v>-53.441734417344</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
       </c>
-      <c r="F22" s="14">
-        <v>2</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>16</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L22" s="15">
         <v>166.666666666667</v>
       </c>
       <c r="M22" s="15">
-        <v>77.777777777777</v>
+        <v>60</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1224,37 +1224,37 @@
         <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H23" s="15">
-        <v>-35.294117647058</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="I23" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J23" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="L23" s="15">
-        <v>32.352941176470</v>
+        <v>30.555555555555</v>
       </c>
       <c r="M23" s="15">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G24" s="14">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.580152671755</v>
+        <v>4.065040650406</v>
       </c>
       <c r="I24" s="14">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="J24" s="14">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="K24" s="15">
-        <v>0.473933649289</v>
+        <v>0.444444444444</v>
       </c>
       <c r="L24" s="15">
-        <v>26.190476190476</v>
+        <v>24.517906336088</v>
       </c>
       <c r="M24" s="15">
-        <v>147.953216374269</v>
+        <v>146.994535519126</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
         <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H25" s="15">
-        <v>-18.181818181818</v>
+        <v>20</v>
       </c>
       <c r="I25" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J25" s="14">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K25" s="15">
-        <v>-41.463414634146</v>
+        <v>-40</v>
       </c>
       <c r="L25" s="15">
-        <v>-42.857142857142</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D26" s="14">
         <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>22.222222222222</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="G26" s="14">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.127659574468</v>
+        <v>15.789473684210</v>
       </c>
       <c r="I26" s="14">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="J26" s="14">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.257328990228</v>
+        <v>2.153846153846</v>
       </c>
       <c r="L26" s="15">
-        <v>3.125</v>
+        <v>8.852459016393</v>
       </c>
       <c r="M26" s="15">
-        <v>14.230769230769</v>
+        <v>17.730496453900</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>4</v>
       </c>
-      <c r="G27" s="14">
-        <v>5</v>
-      </c>
       <c r="H27" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
         <v>22</v>
       </c>
       <c r="J27" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" s="15">
-        <v>10</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L27" s="15">
-        <v>22.222222222222</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,122 +1426,122 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>4</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>5</v>
-      </c>
       <c r="E28" s="15">
-        <v>-60</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J28" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K28" s="15">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>10.526315789473</v>
+        <v>31.578947368421</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I29" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K29" s="15">
-        <v>30</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L29" s="15">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M29" s="15">
-        <v>-13.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N29" s="15">
-        <v>-59.375</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I30" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K30" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="L30" s="15">
-        <v>57.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M30" s="15">
-        <v>-15.384615384615</v>
+        <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-63.333333333333</v>
+        <v>-63.636363636363</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,38 +1551,38 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="14">
         <v>2</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>1236</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>708</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>1682</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>625</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>2746</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>7097</v>

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -890,22 +890,22 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
@@ -923,261 +923,261 @@
         <v>20</v>
       </c>
       <c r="M15" s="15">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-18.181818181818</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-30</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F16" s="14">
         <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H16" s="15">
-        <v>-46.938775510204</v>
+        <v>-48</v>
       </c>
       <c r="I16" s="14">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J16" s="14">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="K16" s="15">
-        <v>-32.885906040268</v>
+        <v>-32.278481012658</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.057553956834</v>
+        <v>-27.210884353741</v>
       </c>
       <c r="M16" s="15">
-        <v>-18.032786885245</v>
+        <v>-16.40625</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.609756097561</v>
+        <v>-75.514874141876</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>41.176470588235</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F17" s="14">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G17" s="14">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.505376344086</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="I17" s="14">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="J17" s="14">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.469534050179</v>
+        <v>-11.643835616438</v>
       </c>
       <c r="L17" s="15">
-        <v>19.323671497584</v>
+        <v>14.159292035398</v>
       </c>
       <c r="M17" s="15">
-        <v>109.322033898305</v>
+        <v>101.5625</v>
       </c>
       <c r="N17" s="15">
-        <v>17.619047619047</v>
+        <v>11.688311688311</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="14">
-        <v>5</v>
-      </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-32</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I18" s="14">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J18" s="14">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.634146341463</v>
+        <v>-14.117647058823</v>
       </c>
       <c r="L18" s="15">
-        <v>-19.540229885057</v>
+        <v>-18.888888888888</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.348314606741</v>
+        <v>-21.505376344086</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.318840579710</v>
+        <v>-87.606112054329</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D19" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E19" s="15">
-        <v>-31.818181818181</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="F19" s="14">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G19" s="14">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.142857142857</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="I19" s="14">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="J19" s="14">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.071428571428</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.861003861003</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="M19" s="15">
-        <v>232</v>
+        <v>225.301204819277</v>
       </c>
       <c r="N19" s="15">
-        <v>52.760736196319</v>
+        <v>50.837988826815</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E20" s="15">
-        <v>-25</v>
+        <v>-62.5</v>
       </c>
       <c r="F20" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G20" s="14">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H20" s="15">
-        <v>-37.704918032786</v>
+        <v>-45.614035087719</v>
       </c>
       <c r="I20" s="14">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J20" s="14">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.269230769230</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L20" s="15">
-        <v>11.842105263157</v>
+        <v>10.691823899371</v>
       </c>
       <c r="M20" s="15">
-        <v>50.442477876106</v>
+        <v>47.899159663865</v>
       </c>
       <c r="N20" s="15">
-        <v>-64.360587002096</v>
+        <v>-64.870259481037</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D21" s="17">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.705882352941</v>
+        <v>-28.358208955223</v>
       </c>
       <c r="F21" s="17">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="G21" s="17">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.402640264026</v>
+        <v>-28.671328671328</v>
       </c>
       <c r="I21" s="17">
-        <v>859</v>
+        <v>907</v>
       </c>
       <c r="J21" s="17">
-        <v>1018</v>
+        <v>1085</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.618860510805</v>
+        <v>-16.405529953917</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.116279069767</v>
+        <v>-0.765864332603</v>
       </c>
       <c r="M21" s="18">
-        <v>59.369202226345</v>
+        <v>58.01393728223</v>
       </c>
       <c r="N21" s="18">
-        <v>-53.441734417344</v>
+        <v>-54.006085192697</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,19 +1201,19 @@
         <v>16</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K22" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>166.666666666667</v>
+        <v>77.777777777777</v>
       </c>
       <c r="M22" s="15">
-        <v>60</v>
+        <v>45.454545454545</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>4</v>
+      </c>
+      <c r="D23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="14">
-        <v>4</v>
-      </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
         <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H23" s="15">
-        <v>-52.380952380952</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="I23" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J23" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K23" s="15">
-        <v>-4.081632653061</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>30.555555555555</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>370</v>
+        <v>292.307692307692</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>65.384615384615</v>
       </c>
       <c r="F24" s="14">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G24" s="14">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H24" s="15">
-        <v>4.065040650406</v>
+        <v>18.75</v>
       </c>
       <c r="I24" s="14">
-        <v>452</v>
+        <v>495</v>
       </c>
       <c r="J24" s="14">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="K24" s="15">
-        <v>0.444444444444</v>
+        <v>3.991596638655</v>
       </c>
       <c r="L24" s="15">
-        <v>24.517906336088</v>
+        <v>27.906976744186</v>
       </c>
       <c r="M24" s="15">
-        <v>146.994535519126</v>
+        <v>159.162303664921</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
         <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H25" s="15">
-        <v>20</v>
+        <v>41.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J25" s="14">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K25" s="15">
-        <v>-40</v>
+        <v>-38.202247191011</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.333333333333</v>
+        <v>-43.877551020408</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="F26" s="14">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G26" s="14">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="H26" s="15">
-        <v>15.789473684210</v>
+        <v>2.912621359223</v>
       </c>
       <c r="I26" s="14">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="J26" s="14">
-        <v>325</v>
+        <v>359</v>
       </c>
       <c r="K26" s="15">
-        <v>2.153846153846</v>
+        <v>-2.228412256267</v>
       </c>
       <c r="L26" s="15">
-        <v>8.852459016393</v>
+        <v>10.725552050473</v>
       </c>
       <c r="M26" s="15">
-        <v>17.730496453900</v>
+        <v>16.611295681063</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>22</v>
@@ -1415,10 +1415,10 @@
         <v>4.761904761904</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-40</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H28" s="15">
-        <v>-10</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I28" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K28" s="15">
-        <v>-16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="L28" s="15">
-        <v>31.578947368421</v>
+        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J29" s="14">
         <v>11</v>
       </c>
       <c r="K29" s="15">
-        <v>27.272727272727</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L29" s="15">
-        <v>40</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M29" s="15">
-        <v>-22.222222222222</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="N29" s="15">
-        <v>-60</v>
+        <v>-60.526315789473</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J30" s="14">
         <v>10</v>
       </c>
       <c r="K30" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L30" s="15">
-        <v>71.428571428571</v>
+        <v>62.5</v>
       </c>
       <c r="M30" s="15">
-        <v>-20</v>
+        <v>-18.75</v>
       </c>
       <c r="N30" s="15">
-        <v>-63.636363636363</v>
+        <v>-63.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1576,13 +1576,13 @@
         <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>2</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>1236</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>708</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>1682</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>625</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>2746</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>7097</v>

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -864,69 +864,69 @@
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="14">
         <v>4</v>
       </c>
       <c r="K14" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L14" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M14" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N14" s="15">
-        <v>-54.545454545454</v>
+        <v>-53.846153846153</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-75</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K15" s="15">
-        <v>12.5</v>
+        <v>-5</v>
       </c>
       <c r="L15" s="15">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="M15" s="15">
-        <v>12.5</v>
+        <v>18.75</v>
       </c>
       <c r="N15" s="15">
-        <v>-25</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E16" s="15">
-        <v>-11.111111111111</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G16" s="14">
         <v>50</v>
       </c>
       <c r="H16" s="15">
-        <v>-48</v>
+        <v>-34</v>
       </c>
       <c r="I16" s="14">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="J16" s="14">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="K16" s="15">
-        <v>-32.278481012658</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.210884353741</v>
+        <v>-24.050632911392</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.40625</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.514874141876</v>
+        <v>-74.468085106383</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>-30.769230769230</v>
+        <v>-18.75</v>
       </c>
       <c r="F17" s="14">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G17" s="14">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H17" s="15">
-        <v>-19.512195121951</v>
+        <v>-14.864864864864</v>
       </c>
       <c r="I17" s="14">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="J17" s="14">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.643835616438</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="L17" s="15">
-        <v>14.159292035398</v>
+        <v>11.885245901639</v>
       </c>
       <c r="M17" s="15">
-        <v>101.5625</v>
+        <v>97.826086956521</v>
       </c>
       <c r="N17" s="15">
-        <v>11.688311688311</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-23.809523809523</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I18" s="14">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J18" s="14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.117647058823</v>
+        <v>-12.222222222222</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.888888888888</v>
+        <v>-17.708333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.505376344086</v>
+        <v>-19.387755102040</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.606112054329</v>
+        <v>-87.420382165605</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-19.230769230769</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F19" s="14">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G19" s="14">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.888888888888</v>
+        <v>-25</v>
       </c>
       <c r="I19" s="14">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="J19" s="14">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.764705882352</v>
+        <v>-13.580246913580</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.173913043478</v>
+        <v>-3.780068728522</v>
       </c>
       <c r="M19" s="15">
-        <v>225.301204819277</v>
+        <v>225.581395348837</v>
       </c>
       <c r="N19" s="15">
-        <v>50.837988826815</v>
+        <v>45.833333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E20" s="15">
-        <v>-62.5</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="F20" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G20" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H20" s="15">
-        <v>-45.614035087719</v>
+        <v>-45.762711864406</v>
       </c>
       <c r="I20" s="14">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="J20" s="14">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="K20" s="15">
-        <v>-21.428571428571</v>
+        <v>-24.279835390946</v>
       </c>
       <c r="L20" s="15">
-        <v>10.691823899371</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M20" s="15">
-        <v>47.899159663865</v>
+        <v>53.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-64.870259481037</v>
+        <v>-65.348399246704</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D21" s="17">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E21" s="18">
-        <v>-28.358208955223</v>
+        <v>-35.526315789473</v>
       </c>
       <c r="F21" s="17">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G21" s="17">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.671328671328</v>
+        <v>-28.027681660899</v>
       </c>
       <c r="I21" s="17">
-        <v>907</v>
+        <v>961</v>
       </c>
       <c r="J21" s="17">
-        <v>1085</v>
+        <v>1161</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.405529953917</v>
+        <v>-17.226528854435</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.765864332603</v>
+        <v>-2.138492871690</v>
       </c>
       <c r="M21" s="18">
-        <v>58.01393728223</v>
+        <v>61.512605042016</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.006085192697</v>
+        <v>-54.433380749170</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
@@ -1201,16 +1201,16 @@
         <v>16</v>
       </c>
       <c r="J22" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>33.333333333333</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L22" s="15">
         <v>77.777777777777</v>
       </c>
       <c r="M22" s="15">
-        <v>45.454545454545</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>-40</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>-47.368421052631</v>
+        <v>-31.25</v>
       </c>
       <c r="I23" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J23" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="L23" s="15">
-        <v>41.666666666666</v>
+        <v>45.945945945945</v>
       </c>
       <c r="M23" s="15">
-        <v>292.307692307692</v>
+        <v>285.714285714286</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>65.384615384615</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F24" s="14">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="G24" s="14">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H24" s="15">
-        <v>18.75</v>
+        <v>7.079646017699</v>
       </c>
       <c r="I24" s="14">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="J24" s="14">
-        <v>476</v>
+        <v>510</v>
       </c>
       <c r="K24" s="15">
-        <v>3.991596638655</v>
+        <v>1.764705882352</v>
       </c>
       <c r="L24" s="15">
-        <v>27.906976744186</v>
+        <v>24.759615384615</v>
       </c>
       <c r="M24" s="15">
-        <v>159.162303664921</v>
+        <v>150.724637681159</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
         <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>41.666666666666</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I25" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J25" s="14">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K25" s="15">
-        <v>-38.202247191011</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.877551020408</v>
+        <v>-46.226415094339</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E26" s="15">
-        <v>-38.235294117647</v>
+        <v>-43.902439024390</v>
       </c>
       <c r="F26" s="14">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G26" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H26" s="15">
-        <v>2.912621359223</v>
+        <v>-9.909909909909</v>
       </c>
       <c r="I26" s="14">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="J26" s="14">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.228412256267</v>
+        <v>-6.75</v>
       </c>
       <c r="L26" s="15">
-        <v>10.725552050473</v>
+        <v>7.492795389048</v>
       </c>
       <c r="M26" s="15">
-        <v>16.611295681063</v>
+        <v>17.665615141955</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>4</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-75</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K27" s="15">
-        <v>4.761904761904</v>
+        <v>-8</v>
       </c>
       <c r="L27" s="15">
-        <v>4.761904761904</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H28" s="15">
-        <v>-15.384615384615</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J28" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K28" s="15">
-        <v>-20</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="L28" s="15">
-        <v>40</v>
+        <v>47.619047619047</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,20 +1466,20 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>0</v>
@@ -1488,10 +1488,10 @@
         <v>15</v>
       </c>
       <c r="J29" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K29" s="15">
-        <v>36.363636363636</v>
+        <v>25</v>
       </c>
       <c r="L29" s="15">
         <v>36.363636363636</v>
@@ -1500,27 +1500,27 @@
         <v>-21.052631578947</v>
       </c>
       <c r="N29" s="15">
-        <v>-60.526315789473</v>
+        <v>-63.414634146341</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>0</v>
@@ -1529,10 +1529,10 @@
         <v>13</v>
       </c>
       <c r="J30" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K30" s="15">
-        <v>30</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L30" s="15">
         <v>62.5</v>
@@ -1541,7 +1541,7 @@
         <v>-18.75</v>
       </c>
       <c r="N30" s="15">
-        <v>-63.888888888888</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,14 +1557,14 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-047pct.xlsx
+++ b/data/source/weekly/cs-en-us-047pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -882,7 +882,7 @@
         <v>500</v>
       </c>
       <c r="M14" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="N14" s="15">
         <v>-53.846153846153</v>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>4</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-75</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" s="14">
         <v>20</v>
       </c>
       <c r="K15" s="15">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>18.75</v>
+        <v>25</v>
       </c>
       <c r="M15" s="15">
-        <v>18.75</v>
+        <v>25</v>
       </c>
       <c r="N15" s="15">
-        <v>-24</v>
+        <v>-23.076923076923</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>-7.142857142857</v>
+        <v>10</v>
       </c>
       <c r="F16" s="14">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G16" s="14">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H16" s="15">
-        <v>-34</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="I16" s="14">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="J16" s="14">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="K16" s="15">
-        <v>-30.232558139534</v>
+        <v>-28.021978021978</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.050632911392</v>
+        <v>-24.277456647398</v>
       </c>
       <c r="M16" s="15">
-        <v>-7.692307692307</v>
+        <v>-7.746478873239</v>
       </c>
       <c r="N16" s="15">
-        <v>-74.468085106383</v>
+        <v>-74.4140625</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E17" s="15">
-        <v>-18.75</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="F17" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" s="14">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.864864864864</v>
+        <v>-1.538461538461</v>
       </c>
       <c r="I17" s="14">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="J17" s="14">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.363636363636</v>
+        <v>-11.620795107033</v>
       </c>
       <c r="L17" s="15">
-        <v>11.885245901639</v>
+        <v>10.727969348659</v>
       </c>
       <c r="M17" s="15">
-        <v>97.826086956521</v>
+        <v>100.694444444444</v>
       </c>
       <c r="N17" s="15">
-        <v>9.2</v>
+        <v>7.835820895522</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-10.526315789473</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J18" s="14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K18" s="15">
-        <v>-12.222222222222</v>
+        <v>-14.736842105263</v>
       </c>
       <c r="L18" s="15">
-        <v>-17.708333333333</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M18" s="15">
-        <v>-19.387755102040</v>
+        <v>-24.299065420560</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.420382165605</v>
+        <v>-87.910447761194</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E19" s="15">
-        <v>-55.555555555555</v>
+        <v>-58.620689655172</v>
       </c>
       <c r="F19" s="14">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="H19" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I19" s="14">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="J19" s="14">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.580246913580</v>
+        <v>-16.430594900849</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.780068728522</v>
+        <v>-4.220779220779</v>
       </c>
       <c r="M19" s="15">
-        <v>225.581395348837</v>
+        <v>227.777777777778</v>
       </c>
       <c r="N19" s="15">
-        <v>45.833333333333</v>
+        <v>48.989898989899</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D20" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E20" s="15">
-        <v>-57.894736842105</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F20" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G20" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H20" s="15">
-        <v>-45.762711864406</v>
+        <v>-44.262295081967</v>
       </c>
       <c r="I20" s="14">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="J20" s="14">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="K20" s="15">
-        <v>-24.279835390946</v>
+        <v>-24.124513618677</v>
       </c>
       <c r="L20" s="15">
-        <v>4.545454545454</v>
+        <v>2.094240837696</v>
       </c>
       <c r="M20" s="15">
-        <v>53.333333333333</v>
+        <v>59.836065573770</v>
       </c>
       <c r="N20" s="15">
-        <v>-65.348399246704</v>
+        <v>-65.486725663716</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" s="17">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E21" s="18">
-        <v>-35.526315789473</v>
+        <v>-33.766233766233</v>
       </c>
       <c r="F21" s="17">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G21" s="17">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.027681660899</v>
+        <v>-26.388888888888</v>
       </c>
       <c r="I21" s="17">
-        <v>961</v>
+        <v>1017</v>
       </c>
       <c r="J21" s="17">
-        <v>1161</v>
+        <v>1238</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.226528854435</v>
+        <v>-17.851373182552</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.138492871690</v>
+        <v>-3.050524308865</v>
       </c>
       <c r="M21" s="18">
-        <v>61.512605042016</v>
+        <v>61.685214626391</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.433380749170</v>
+        <v>-54.840142095914</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,17 +1182,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1207,10 +1207,10 @@
         <v>23.076923076923</v>
       </c>
       <c r="L22" s="15">
-        <v>77.777777777777</v>
+        <v>60</v>
       </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>3</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="14">
+        <v>9</v>
+      </c>
+      <c r="G23" s="14">
+        <v>15</v>
+      </c>
+      <c r="H23" s="15">
         <v>-40</v>
-      </c>
-      <c r="F23" s="14">
-        <v>11</v>
-      </c>
-      <c r="G23" s="14">
-        <v>16</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-31.25</v>
       </c>
       <c r="I23" s="14">
         <v>54</v>
       </c>
       <c r="J23" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K23" s="15">
-        <v>-3.571428571428</v>
+        <v>-10</v>
       </c>
       <c r="L23" s="15">
-        <v>45.945945945945</v>
+        <v>42.105263157894</v>
       </c>
       <c r="M23" s="15">
-        <v>285.714285714286</v>
+        <v>237.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-29.411764705882</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G24" s="14">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H24" s="15">
-        <v>7.079646017699</v>
+        <v>10.344827586206</v>
       </c>
       <c r="I24" s="14">
-        <v>519</v>
+        <v>549</v>
       </c>
       <c r="J24" s="14">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="K24" s="15">
-        <v>1.764705882352</v>
+        <v>2.044609665427</v>
       </c>
       <c r="L24" s="15">
-        <v>24.759615384615</v>
+        <v>23.648648648648</v>
       </c>
       <c r="M24" s="15">
-        <v>150.724637681159</v>
+        <v>155.348837209302</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>1</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
+        <v>9</v>
+      </c>
+      <c r="G25" s="14">
         <v>14</v>
       </c>
-      <c r="G25" s="14">
-        <v>13</v>
-      </c>
       <c r="H25" s="15">
-        <v>7.692307692307</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I25" s="14">
         <v>57</v>
       </c>
       <c r="J25" s="14">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K25" s="15">
-        <v>-38.709677419354</v>
+        <v>-40.625</v>
       </c>
       <c r="L25" s="15">
-        <v>-46.226415094339</v>
+        <v>-52.100840336134</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>-43.902439024390</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F26" s="14">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G26" s="14">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.909909909909</v>
+        <v>-18.260869565217</v>
       </c>
       <c r="I26" s="14">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="J26" s="14">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.75</v>
+        <v>-7.819905213270</v>
       </c>
       <c r="L26" s="15">
-        <v>7.492795389048</v>
+        <v>6.284153005464</v>
       </c>
       <c r="M26" s="15">
-        <v>17.665615141955</v>
+        <v>12.753623188405</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,10 +1388,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1403,16 +1403,16 @@
         <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K27" s="15">
-        <v>-8</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L27" s="15">
-        <v>4.545454545454</v>
+        <v>4.347826086956</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I28" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J28" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.421052631578</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="L28" s="15">
-        <v>47.619047619047</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1470,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
         <v>-100</v>
@@ -1479,28 +1479,28 @@
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>15</v>
       </c>
       <c r="J29" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K29" s="15">
-        <v>25</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L29" s="15">
         <v>36.363636363636</v>
       </c>
       <c r="M29" s="15">
-        <v>-21.052631578947</v>
+        <v>-25</v>
       </c>
       <c r="N29" s="15">
-        <v>-63.414634146341</v>
+        <v>-67.391304347826</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,28 +1520,28 @@
         <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I30" s="14">
         <v>13</v>
       </c>
       <c r="J30" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K30" s="15">
-        <v>18.181818181818</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L30" s="15">
         <v>62.5</v>
       </c>
       <c r="M30" s="15">
-        <v>-18.75</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N30" s="15">
-        <v>-66.666666666666</v>
+        <v>-69.767441860465</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
